--- a/Risultati/Excel/Risultati.xlsx
+++ b/Risultati/Excel/Risultati.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gassi\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gassi\OneDrive\Desktop\Risultati\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BC47F5D-D10F-42B0-A0EC-50FFC867276F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2545B6-E722-42EC-8969-1A95739215AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B4842C5C-3131-4712-BA35-63F4B6CA9F3B}"/>
   </bookViews>
@@ -50,9 +50,6 @@
     <t>Feature Selection</t>
   </si>
   <si>
-    <t>RAW</t>
-  </si>
-  <si>
     <t>Top 1024</t>
   </si>
   <si>
@@ -83,9 +80,6 @@
     <t>0.7147</t>
   </si>
   <si>
-    <t>SEMANTIC</t>
-  </si>
-  <si>
     <t>0.7959</t>
   </si>
   <si>
@@ -339,6 +333,12 @@
   </si>
   <si>
     <t>[[12540, 954], [5307, 8234]]</t>
+  </si>
+  <si>
+    <t>ORIGINAL</t>
+  </si>
+  <si>
+    <t>EMBEDDING</t>
   </si>
 </sst>
 </file>
@@ -388,12 +388,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -411,10 +414,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -746,7 +745,7 @@
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -758,37 +757,37 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="O1" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -796,87 +795,88 @@
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="D2" s="2">
         <v>2381</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
       <c r="B3" s="2">
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="D3" s="2">
         <v>2381</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
@@ -884,43 +884,43 @@
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="D4" s="2">
         <v>2381</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
@@ -928,43 +928,43 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="D5" s="2">
         <v>2381</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
@@ -972,43 +972,43 @@
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="L6" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -1016,43 +1016,43 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="N7" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
@@ -1060,607 +1060,607 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O8" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B10" s="2">
         <v>3</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="D10" s="2">
         <v>2381</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B11" s="2">
         <v>5</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="D11" s="2">
         <v>2381</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B12" s="2">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="D12" s="2">
         <v>2381</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B13" s="2">
         <v>9</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="D13" s="2">
         <v>2381</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B15" s="2">
         <v>3</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="D15" s="2">
         <v>2381</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B16" s="2">
         <v>5</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="D16" s="2">
         <v>2381</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K16" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="L16" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B17" s="2">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="D17" s="2">
         <v>2381</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I17" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="L17" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B18" s="2">
         <v>9</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="D18" s="2">
         <v>2381</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B20" s="2">
         <v>3</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="D20" s="2">
         <v>2381</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B21" s="2">
         <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="D21" s="2">
         <v>2381</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B22" s="2">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="D22" s="2">
         <v>2381</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B23" s="2">
         <v>9</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="D23" s="2">
         <v>2381</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="J23" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
